--- a/uploads/student_mapping.xlsx
+++ b/uploads/student_mapping.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{41E5D626-8C31-476B-8E1C-BC465E49BAF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{493DB11E-33F7-49B1-930B-ACC46B7B4D93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3F4B078A-DBEB-44A2-8A72-81311EF27125}"/>
+    <workbookView xWindow="5760" yWindow="3360" windowWidth="17280" windowHeight="8880" xr2:uid="{3F4B078A-DBEB-44A2-8A72-81311EF27125}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -59,10 +59,10 @@
     <t>Benita</t>
   </si>
   <si>
-    <t>S8_CSE_A</t>
-  </si>
-  <si>
     <t>S2_ME</t>
+  </si>
+  <si>
+    <t>S8_CSE</t>
   </si>
 </sst>
 </file>
@@ -121,7 +121,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -485,7 +485,7 @@
         <v>4</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -496,7 +496,7 @@
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
